--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>144200</v>
+        <v>142100</v>
       </c>
       <c r="E8" s="3">
-        <v>137300</v>
+        <v>145200</v>
       </c>
       <c r="F8" s="3">
-        <v>153800</v>
+        <v>138200</v>
       </c>
       <c r="G8" s="3">
-        <v>125900</v>
+        <v>154900</v>
       </c>
       <c r="H8" s="3">
-        <v>115400</v>
+        <v>126700</v>
       </c>
       <c r="I8" s="3">
-        <v>102600</v>
+        <v>116200</v>
       </c>
       <c r="J8" s="3">
+        <v>103300</v>
+      </c>
+      <c r="K8" s="3">
         <v>140700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>117100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>90700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>68700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>72400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>66600</v>
+        <v>65900</v>
       </c>
       <c r="E9" s="3">
-        <v>66600</v>
+        <v>67000</v>
       </c>
       <c r="F9" s="3">
         <v>67000</v>
       </c>
       <c r="G9" s="3">
-        <v>64500</v>
+        <v>67500</v>
       </c>
       <c r="H9" s="3">
-        <v>60300</v>
+        <v>65000</v>
       </c>
       <c r="I9" s="3">
-        <v>56300</v>
+        <v>60700</v>
       </c>
       <c r="J9" s="3">
+        <v>56700</v>
+      </c>
+      <c r="K9" s="3">
         <v>74500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>77600</v>
+        <v>76300</v>
       </c>
       <c r="E10" s="3">
-        <v>70700</v>
+        <v>78100</v>
       </c>
       <c r="F10" s="3">
-        <v>86800</v>
+        <v>71200</v>
       </c>
       <c r="G10" s="3">
-        <v>61400</v>
+        <v>87400</v>
       </c>
       <c r="H10" s="3">
-        <v>55200</v>
+        <v>61800</v>
       </c>
       <c r="I10" s="3">
-        <v>46300</v>
+        <v>55600</v>
       </c>
       <c r="J10" s="3">
+        <v>46600</v>
+      </c>
+      <c r="K10" s="3">
         <v>66300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>53500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>32600</v>
+        <v>34700</v>
       </c>
       <c r="E12" s="3">
-        <v>25300</v>
+        <v>32800</v>
       </c>
       <c r="F12" s="3">
-        <v>29300</v>
+        <v>25400</v>
       </c>
       <c r="G12" s="3">
-        <v>22200</v>
+        <v>29500</v>
       </c>
       <c r="H12" s="3">
-        <v>30900</v>
+        <v>22300</v>
       </c>
       <c r="I12" s="3">
-        <v>23000</v>
+        <v>31100</v>
       </c>
       <c r="J12" s="3">
+        <v>23100</v>
+      </c>
+      <c r="K12" s="3">
         <v>28700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12900</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1118,14 +1138,17 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1177,14 +1200,17 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>189400</v>
+        <v>190800</v>
       </c>
       <c r="E17" s="3">
-        <v>167200</v>
+        <v>190700</v>
       </c>
       <c r="F17" s="3">
-        <v>183700</v>
+        <v>168300</v>
       </c>
       <c r="G17" s="3">
-        <v>164400</v>
+        <v>184900</v>
       </c>
       <c r="H17" s="3">
-        <v>179000</v>
+        <v>165500</v>
       </c>
       <c r="I17" s="3">
-        <v>192100</v>
+        <v>180300</v>
       </c>
       <c r="J17" s="3">
+        <v>193400</v>
+      </c>
+      <c r="K17" s="3">
         <v>192500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>162900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>117900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>86900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>61700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>77200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-45200</v>
+        <v>-48700</v>
       </c>
       <c r="E18" s="3">
-        <v>-29900</v>
+        <v>-45500</v>
       </c>
       <c r="F18" s="3">
-        <v>-29900</v>
+        <v>-30100</v>
       </c>
       <c r="G18" s="3">
-        <v>-38500</v>
+        <v>-30100</v>
       </c>
       <c r="H18" s="3">
-        <v>-63600</v>
+        <v>-38700</v>
       </c>
       <c r="I18" s="3">
-        <v>-89500</v>
+        <v>-64000</v>
       </c>
       <c r="J18" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-51800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-45800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-49800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-49200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-42700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,67 +1377,71 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E20" s="3">
         <v>7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
-        <v>5000</v>
-      </c>
       <c r="J20" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1438,32 +1475,35 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-9700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-34200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1515,132 +1555,141 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-38200</v>
+        <v>-38700</v>
       </c>
       <c r="E23" s="3">
-        <v>-24000</v>
+        <v>-38500</v>
       </c>
       <c r="F23" s="3">
-        <v>-24400</v>
+        <v>-24200</v>
       </c>
       <c r="G23" s="3">
-        <v>-40700</v>
+        <v>-24600</v>
       </c>
       <c r="H23" s="3">
-        <v>-66400</v>
+        <v>-41000</v>
       </c>
       <c r="I23" s="3">
-        <v>-84500</v>
+        <v>-66800</v>
       </c>
       <c r="J23" s="3">
+        <v>-85100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-52500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-45400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-37300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-43900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-38500</v>
+        <v>-38700</v>
       </c>
       <c r="E26" s="3">
-        <v>-24700</v>
+        <v>-38800</v>
       </c>
       <c r="F26" s="3">
-        <v>-24800</v>
+        <v>-24900</v>
       </c>
       <c r="G26" s="3">
-        <v>-41100</v>
+        <v>-25000</v>
       </c>
       <c r="H26" s="3">
-        <v>-67200</v>
+        <v>-41400</v>
       </c>
       <c r="I26" s="3">
-        <v>-84800</v>
+        <v>-67700</v>
       </c>
       <c r="J26" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-52900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-37300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-38600</v>
+        <v>-38700</v>
       </c>
       <c r="E27" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-25000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-41400</v>
-      </c>
       <c r="H27" s="3">
-        <v>-67200</v>
+        <v>-41700</v>
       </c>
       <c r="I27" s="3">
-        <v>-84800</v>
+        <v>-67700</v>
       </c>
       <c r="J27" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-52900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-71100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-36200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-57900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-62300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1928,14 +1989,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
-        <v>-5000</v>
-      </c>
       <c r="J32" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-38600</v>
+        <v>-38700</v>
       </c>
       <c r="E33" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-25000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-41400</v>
-      </c>
       <c r="H33" s="3">
-        <v>-67200</v>
+        <v>-41700</v>
       </c>
       <c r="I33" s="3">
-        <v>-84800</v>
+        <v>-67700</v>
       </c>
       <c r="J33" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-52900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-71100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-36200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-41300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-57900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-62300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-38600</v>
+        <v>-38700</v>
       </c>
       <c r="E35" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-25000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-41400</v>
-      </c>
       <c r="H35" s="3">
-        <v>-67200</v>
+        <v>-41700</v>
       </c>
       <c r="I35" s="3">
-        <v>-84800</v>
+        <v>-67700</v>
       </c>
       <c r="J35" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-52900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-71100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-36200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-41300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-57900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-62300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,50 +2484,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>557000</v>
+        <v>435600</v>
       </c>
       <c r="E41" s="3">
-        <v>576100</v>
+        <v>560800</v>
       </c>
       <c r="F41" s="3">
-        <v>624900</v>
+        <v>580000</v>
       </c>
       <c r="G41" s="3">
-        <v>469100</v>
+        <v>629200</v>
       </c>
       <c r="H41" s="3">
-        <v>310600</v>
+        <v>472300</v>
       </c>
       <c r="I41" s="3">
-        <v>330400</v>
+        <v>312700</v>
       </c>
       <c r="J41" s="3">
+        <v>332700</v>
+      </c>
+      <c r="K41" s="3">
         <v>297900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>125700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>862500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>96800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2457,50 +2544,53 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>293400</v>
+        <v>350500</v>
       </c>
       <c r="E42" s="3">
-        <v>288000</v>
+        <v>295400</v>
       </c>
       <c r="F42" s="3">
-        <v>239700</v>
+        <v>290000</v>
       </c>
       <c r="G42" s="3">
-        <v>445600</v>
+        <v>241300</v>
       </c>
       <c r="H42" s="3">
-        <v>497100</v>
+        <v>448600</v>
       </c>
       <c r="I42" s="3">
-        <v>613500</v>
+        <v>500500</v>
       </c>
       <c r="J42" s="3">
+        <v>617700</v>
+      </c>
+      <c r="K42" s="3">
         <v>698000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>754400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>691000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>257100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>297700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>374700</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2516,50 +2606,53 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>105100</v>
+        <v>88600</v>
       </c>
       <c r="E43" s="3">
+        <v>105800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>108100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>119400</v>
+      </c>
+      <c r="H43" s="3">
         <v>107400</v>
       </c>
-      <c r="F43" s="3">
-        <v>118600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>106700</v>
-      </c>
-      <c r="H43" s="3">
-        <v>120300</v>
-      </c>
       <c r="I43" s="3">
-        <v>117400</v>
+        <v>121100</v>
       </c>
       <c r="J43" s="3">
+        <v>118200</v>
+      </c>
+      <c r="K43" s="3">
         <v>117300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>85700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>72500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>76100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2628,56 +2724,59 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
+      <c r="T44" s="3">
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33100</v>
+        <v>46000</v>
       </c>
       <c r="E45" s="3">
-        <v>29700</v>
+        <v>33300</v>
       </c>
       <c r="F45" s="3">
-        <v>27500</v>
+        <v>29900</v>
       </c>
       <c r="G45" s="3">
-        <v>31900</v>
+        <v>27700</v>
       </c>
       <c r="H45" s="3">
-        <v>64800</v>
+        <v>32100</v>
       </c>
       <c r="I45" s="3">
-        <v>55800</v>
+        <v>65200</v>
       </c>
       <c r="J45" s="3">
+        <v>56200</v>
+      </c>
+      <c r="K45" s="3">
         <v>37600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>194100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2693,50 +2792,53 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>988600</v>
+        <v>920600</v>
       </c>
       <c r="E46" s="3">
-        <v>1001100</v>
+        <v>995300</v>
       </c>
       <c r="F46" s="3">
-        <v>1010700</v>
+        <v>1007900</v>
       </c>
       <c r="G46" s="3">
-        <v>1053300</v>
+        <v>1017600</v>
       </c>
       <c r="H46" s="3">
-        <v>992800</v>
+        <v>1060500</v>
       </c>
       <c r="I46" s="3">
-        <v>1117200</v>
+        <v>999600</v>
       </c>
       <c r="J46" s="3">
+        <v>1124800</v>
+      </c>
+      <c r="K46" s="3">
         <v>1150800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1183400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1096600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1206600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>517800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>536200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2752,34 +2854,37 @@
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="E47" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>1700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2600</v>
       </c>
       <c r="J47" s="3">
         <v>2600</v>
       </c>
       <c r="K47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="L47" s="3">
         <v>2800</v>
@@ -2787,8 +2892,8 @@
       <c r="M47" s="3">
         <v>2800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
+      <c r="N47" s="3">
+        <v>2800</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
@@ -2811,50 +2916,53 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12600</v>
+        <v>7700</v>
       </c>
       <c r="E48" s="3">
-        <v>14000</v>
+        <v>12700</v>
       </c>
       <c r="F48" s="3">
-        <v>14800</v>
+        <v>14100</v>
       </c>
       <c r="G48" s="3">
-        <v>16200</v>
+        <v>14900</v>
       </c>
       <c r="H48" s="3">
-        <v>18100</v>
+        <v>16300</v>
       </c>
       <c r="I48" s="3">
-        <v>19900</v>
+        <v>18200</v>
       </c>
       <c r="J48" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K48" s="3">
         <v>18800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2870,50 +2978,53 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44600</v>
+        <v>44100</v>
       </c>
       <c r="E49" s="3">
-        <v>28000</v>
+        <v>44900</v>
       </c>
       <c r="F49" s="3">
-        <v>28500</v>
+        <v>28200</v>
       </c>
       <c r="G49" s="3">
-        <v>29300</v>
+        <v>28700</v>
       </c>
       <c r="H49" s="3">
-        <v>18200</v>
+        <v>29500</v>
       </c>
       <c r="I49" s="3">
-        <v>18900</v>
+        <v>18300</v>
       </c>
       <c r="J49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K49" s="3">
         <v>19600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,16 +3164,19 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4100</v>
+        <v>3200</v>
       </c>
       <c r="E52" s="3">
-        <v>3100</v>
+        <v>4200</v>
       </c>
       <c r="F52" s="3">
         <v>3100</v>
@@ -3065,32 +3185,32 @@
         <v>3100</v>
       </c>
       <c r="H52" s="3">
-        <v>124300</v>
+        <v>3100</v>
       </c>
       <c r="I52" s="3">
+        <v>125100</v>
+      </c>
+      <c r="J52" s="3">
         <v>2000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>106400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,50 +3288,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1054000</v>
+        <v>979800</v>
       </c>
       <c r="E54" s="3">
-        <v>1050400</v>
+        <v>1061200</v>
       </c>
       <c r="F54" s="3">
-        <v>1057200</v>
+        <v>1057500</v>
       </c>
       <c r="G54" s="3">
-        <v>1101800</v>
+        <v>1064400</v>
       </c>
       <c r="H54" s="3">
-        <v>1155100</v>
+        <v>1109300</v>
       </c>
       <c r="I54" s="3">
-        <v>1160600</v>
+        <v>1162900</v>
       </c>
       <c r="J54" s="3">
+        <v>1168500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1215800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1241800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1221100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1249000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>523600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>542800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,50 +3400,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>157000</v>
+        <v>132600</v>
       </c>
       <c r="E57" s="3">
-        <v>138300</v>
+        <v>158000</v>
       </c>
       <c r="F57" s="3">
-        <v>126500</v>
+        <v>139200</v>
       </c>
       <c r="G57" s="3">
         <v>127400</v>
       </c>
       <c r="H57" s="3">
-        <v>167500</v>
+        <v>128300</v>
       </c>
       <c r="I57" s="3">
-        <v>141300</v>
+        <v>168700</v>
       </c>
       <c r="J57" s="3">
+        <v>142300</v>
+      </c>
+      <c r="K57" s="3">
         <v>141700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>107200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>86400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>57700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3382,56 +3516,59 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>131700</v>
+        <v>133100</v>
       </c>
       <c r="E59" s="3">
-        <v>129800</v>
+        <v>132600</v>
       </c>
       <c r="F59" s="3">
-        <v>125500</v>
+        <v>130600</v>
       </c>
       <c r="G59" s="3">
-        <v>137300</v>
+        <v>126300</v>
       </c>
       <c r="H59" s="3">
-        <v>124600</v>
+        <v>138200</v>
       </c>
       <c r="I59" s="3">
-        <v>117400</v>
+        <v>125400</v>
       </c>
       <c r="J59" s="3">
+        <v>118200</v>
+      </c>
+      <c r="K59" s="3">
         <v>120300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>113100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>90900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>71400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3447,50 +3584,53 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>288700</v>
+        <v>265700</v>
       </c>
       <c r="E60" s="3">
-        <v>268000</v>
+        <v>290600</v>
       </c>
       <c r="F60" s="3">
-        <v>252000</v>
+        <v>269900</v>
       </c>
       <c r="G60" s="3">
-        <v>264800</v>
+        <v>253700</v>
       </c>
       <c r="H60" s="3">
-        <v>292100</v>
+        <v>266600</v>
       </c>
       <c r="I60" s="3">
-        <v>258700</v>
+        <v>294100</v>
       </c>
       <c r="J60" s="3">
+        <v>260500</v>
+      </c>
+      <c r="K60" s="3">
         <v>262000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>227900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>202300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>177200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>141200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>125100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3506,8 +3646,11 @@
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,50 +3708,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>27300</v>
+        <v>21500</v>
       </c>
       <c r="E62" s="3">
-        <v>18500</v>
+        <v>27500</v>
       </c>
       <c r="F62" s="3">
-        <v>18900</v>
+        <v>18600</v>
       </c>
       <c r="G62" s="3">
-        <v>20000</v>
+        <v>19100</v>
       </c>
       <c r="H62" s="3">
-        <v>22600</v>
+        <v>20100</v>
       </c>
       <c r="I62" s="3">
-        <v>23500</v>
+        <v>22800</v>
       </c>
       <c r="J62" s="3">
+        <v>23600</v>
+      </c>
+      <c r="K62" s="3">
         <v>23400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,50 +3956,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>326200</v>
+        <v>299500</v>
       </c>
       <c r="E66" s="3">
-        <v>293700</v>
+        <v>328400</v>
       </c>
       <c r="F66" s="3">
-        <v>276500</v>
+        <v>295700</v>
       </c>
       <c r="G66" s="3">
-        <v>289100</v>
+        <v>278400</v>
       </c>
       <c r="H66" s="3">
-        <v>316900</v>
+        <v>291000</v>
       </c>
       <c r="I66" s="3">
-        <v>283800</v>
+        <v>319100</v>
       </c>
       <c r="J66" s="3">
+        <v>285700</v>
+      </c>
+      <c r="K66" s="3">
         <v>286400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>245200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>209800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>184300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>141200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>125200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,14 +4205,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>1098500</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1127600</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4054,14 +4222,17 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-      <c r="T70" s="3" t="s">
-        <v>4</v>
+      <c r="T70" s="3">
+        <v>0</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,8 +4290,11 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4130,39 +4304,39 @@
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="3">
-        <v>-1085600</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1019300</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-1093000</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-1026300</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-867300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-688800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-694400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,50 +4538,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>727900</v>
+        <v>680400</v>
       </c>
       <c r="E76" s="3">
-        <v>756700</v>
+        <v>732800</v>
       </c>
       <c r="F76" s="3">
-        <v>780700</v>
+        <v>761800</v>
       </c>
       <c r="G76" s="3">
-        <v>812800</v>
+        <v>786000</v>
       </c>
       <c r="H76" s="3">
-        <v>838100</v>
+        <v>818300</v>
       </c>
       <c r="I76" s="3">
-        <v>876800</v>
+        <v>843800</v>
       </c>
       <c r="J76" s="3">
+        <v>882700</v>
+      </c>
+      <c r="K76" s="3">
         <v>929400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>996600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1011300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1064700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-716100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-709900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-38600</v>
+        <v>-38700</v>
       </c>
       <c r="E81" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-25000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-41400</v>
-      </c>
       <c r="H81" s="3">
-        <v>-67200</v>
+        <v>-41700</v>
       </c>
       <c r="I81" s="3">
-        <v>-84800</v>
+        <v>-67700</v>
       </c>
       <c r="J81" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-52900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-71100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-36200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-41300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-57900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-62300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4663,8 +4862,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,8 +5187,11 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5017,8 +5234,8 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
@@ -5032,8 +5249,11 @@
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5099,8 +5320,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5459,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5276,8 +5506,8 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,8 +5793,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5594,8 +5840,8 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
@@ -5609,8 +5855,11 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5653,8 +5902,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
@@ -5668,8 +5917,11 @@
       <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5712,8 +5964,8 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
@@ -5725,6 +5977,9 @@
         <v>4</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,289 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>142100</v>
+        <v>132800</v>
       </c>
       <c r="E8" s="3">
-        <v>145200</v>
+        <v>157300</v>
       </c>
       <c r="F8" s="3">
-        <v>138200</v>
+        <v>141200</v>
       </c>
       <c r="G8" s="3">
-        <v>154900</v>
+        <v>144300</v>
       </c>
       <c r="H8" s="3">
-        <v>126700</v>
+        <v>137400</v>
       </c>
       <c r="I8" s="3">
+        <v>153900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>126000</v>
+      </c>
+      <c r="K8" s="3">
         <v>116200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>103300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>140700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>117100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>90700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>68700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>72400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>55900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>38500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>29700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>34500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>27100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>65900</v>
+        <v>57700</v>
       </c>
       <c r="E9" s="3">
-        <v>67000</v>
+        <v>64300</v>
       </c>
       <c r="F9" s="3">
-        <v>67000</v>
+        <v>65400</v>
       </c>
       <c r="G9" s="3">
-        <v>67500</v>
+        <v>66600</v>
       </c>
       <c r="H9" s="3">
-        <v>65000</v>
+        <v>66600</v>
       </c>
       <c r="I9" s="3">
+        <v>67100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>64600</v>
+      </c>
+      <c r="K9" s="3">
         <v>60700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>56700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>74500</v>
       </c>
       <c r="L9" s="3">
         <v>56700</v>
       </c>
       <c r="M9" s="3">
+        <v>74500</v>
+      </c>
+      <c r="N9" s="3">
+        <v>56700</v>
+      </c>
+      <c r="O9" s="3">
         <v>37200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>29500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>47500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>17300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>15500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>76300</v>
+        <v>75100</v>
       </c>
       <c r="E10" s="3">
-        <v>78100</v>
+        <v>93000</v>
       </c>
       <c r="F10" s="3">
-        <v>71200</v>
+        <v>75800</v>
       </c>
       <c r="G10" s="3">
-        <v>87400</v>
+        <v>77700</v>
       </c>
       <c r="H10" s="3">
-        <v>61800</v>
+        <v>70800</v>
       </c>
       <c r="I10" s="3">
+        <v>86800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>61400</v>
+      </c>
+      <c r="K10" s="3">
         <v>55600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>46600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>60400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>53500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>39200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>46400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-1300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>12400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>19000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>13000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +986,78 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>34700</v>
+        <v>27300</v>
       </c>
       <c r="E12" s="3">
-        <v>32800</v>
+        <v>32100</v>
       </c>
       <c r="F12" s="3">
-        <v>25400</v>
+        <v>34500</v>
       </c>
       <c r="G12" s="3">
-        <v>29500</v>
+        <v>32600</v>
       </c>
       <c r="H12" s="3">
-        <v>22300</v>
+        <v>25300</v>
       </c>
       <c r="I12" s="3">
+        <v>29400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K12" s="3">
         <v>31100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>23100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>28700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>26200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>17100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>15300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>11500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>22600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>24600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>13700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>13900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>12900</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1118,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1141,14 +1180,20 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1203,14 +1248,20 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1281,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>190800</v>
+        <v>163800</v>
       </c>
       <c r="E17" s="3">
-        <v>190700</v>
+        <v>181900</v>
       </c>
       <c r="F17" s="3">
-        <v>168300</v>
+        <v>189600</v>
       </c>
       <c r="G17" s="3">
-        <v>184900</v>
+        <v>189500</v>
       </c>
       <c r="H17" s="3">
-        <v>165500</v>
+        <v>167300</v>
       </c>
       <c r="I17" s="3">
+        <v>183800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>164500</v>
+      </c>
+      <c r="K17" s="3">
         <v>180300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>193400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>192500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>162900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>140600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>117900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>86900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>74900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>61700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>63000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>77200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-48700</v>
+        <v>-31000</v>
       </c>
       <c r="E18" s="3">
-        <v>-45500</v>
+        <v>-24600</v>
       </c>
       <c r="F18" s="3">
-        <v>-30100</v>
+        <v>-48400</v>
       </c>
       <c r="G18" s="3">
-        <v>-30100</v>
+        <v>-45200</v>
       </c>
       <c r="H18" s="3">
-        <v>-38700</v>
+        <v>-29900</v>
       </c>
       <c r="I18" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-64000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-90100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-51800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-45800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-49800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-49200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-14500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-23200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-33300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-42700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,70 +1443,78 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F20" s="3">
         <v>9900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>7500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>6100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>5400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1478,32 +1551,38 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-9700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-34200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1558,138 +1637,156 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-38700</v>
+        <v>-22700</v>
       </c>
       <c r="E23" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-38500</v>
       </c>
-      <c r="F23" s="3">
-        <v>-24200</v>
-      </c>
       <c r="G23" s="3">
-        <v>-24600</v>
+        <v>-38200</v>
       </c>
       <c r="H23" s="3">
-        <v>-41000</v>
+        <v>-24100</v>
       </c>
       <c r="I23" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-66800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-85100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-52500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-38300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-45400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-46600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-12500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-17200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-31700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-37300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-43900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>700</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1847,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-38700</v>
+        <v>-22900</v>
       </c>
       <c r="E26" s="3">
-        <v>-38800</v>
+        <v>-14200</v>
       </c>
       <c r="F26" s="3">
-        <v>-24900</v>
+        <v>-38500</v>
       </c>
       <c r="G26" s="3">
-        <v>-25000</v>
+        <v>-38600</v>
       </c>
       <c r="H26" s="3">
-        <v>-41400</v>
+        <v>-24700</v>
       </c>
       <c r="I26" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-67700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-85400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-52900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-38400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-45600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-46600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-12500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-17100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-31800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-37300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="G27" s="3">
         <v>-38700</v>
       </c>
-      <c r="E27" s="3">
-        <v>-38900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-25200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-25000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-41700</v>
+        <v>-25100</v>
       </c>
       <c r="I27" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-67700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-85400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-52900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-38400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-45600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-71100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-36200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-42500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-57900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-62300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +2051,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1992,14 +2113,20 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2187,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2255,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-9900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-7500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-6100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-5400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="G33" s="3">
         <v>-38700</v>
       </c>
-      <c r="E33" s="3">
-        <v>-38900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-25200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-25000</v>
-      </c>
       <c r="H33" s="3">
-        <v>-41700</v>
+        <v>-25100</v>
       </c>
       <c r="I33" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-67700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-85400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-52900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-38400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-45600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-71100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-36200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-42500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-57900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-62300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2459,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="G35" s="3">
         <v>-38700</v>
       </c>
-      <c r="E35" s="3">
-        <v>-38900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-25200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-25000</v>
-      </c>
       <c r="H35" s="3">
-        <v>-41700</v>
+        <v>-25100</v>
       </c>
       <c r="I35" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-67700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-85400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-52900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-38400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-45600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-71100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-36200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-42500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-57900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-62300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2630,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2656,58 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>435600</v>
+        <v>303200</v>
       </c>
       <c r="E41" s="3">
-        <v>560800</v>
+        <v>291100</v>
       </c>
       <c r="F41" s="3">
-        <v>580000</v>
+        <v>432900</v>
       </c>
       <c r="G41" s="3">
-        <v>629200</v>
+        <v>557300</v>
       </c>
       <c r="H41" s="3">
-        <v>472300</v>
+        <v>576400</v>
       </c>
       <c r="I41" s="3">
+        <v>625300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>469400</v>
+      </c>
+      <c r="K41" s="3">
         <v>312700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>332700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>297900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>208600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>125700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>862500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>133300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>96800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2547,56 +2720,62 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>350500</v>
+        <v>417600</v>
       </c>
       <c r="E42" s="3">
-        <v>295400</v>
+        <v>463700</v>
       </c>
       <c r="F42" s="3">
-        <v>290000</v>
+        <v>348300</v>
       </c>
       <c r="G42" s="3">
-        <v>241300</v>
+        <v>293600</v>
       </c>
       <c r="H42" s="3">
-        <v>448600</v>
+        <v>288200</v>
       </c>
       <c r="I42" s="3">
+        <v>239800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>445800</v>
+      </c>
+      <c r="K42" s="3">
         <v>500500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>617700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>698000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>754400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>691000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>257100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>297700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>374700</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2609,56 +2788,62 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>88600</v>
+        <v>92500</v>
       </c>
       <c r="E43" s="3">
-        <v>105800</v>
+        <v>94400</v>
       </c>
       <c r="F43" s="3">
-        <v>108100</v>
+        <v>88000</v>
       </c>
       <c r="G43" s="3">
-        <v>119400</v>
+        <v>105200</v>
       </c>
       <c r="H43" s="3">
         <v>107400</v>
       </c>
       <c r="I43" s="3">
+        <v>118700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>106800</v>
+      </c>
+      <c r="K43" s="3">
         <v>121100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>118200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>117300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>102000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>85700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>72500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>76100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>58100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2671,8 +2856,14 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2727,62 +2918,68 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>46000</v>
+        <v>33100</v>
       </c>
       <c r="E45" s="3">
-        <v>33300</v>
+        <v>32100</v>
       </c>
       <c r="F45" s="3">
-        <v>29900</v>
+        <v>45700</v>
       </c>
       <c r="G45" s="3">
-        <v>27700</v>
+        <v>33100</v>
       </c>
       <c r="H45" s="3">
-        <v>32100</v>
+        <v>29700</v>
       </c>
       <c r="I45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>31900</v>
+      </c>
+      <c r="K45" s="3">
         <v>65200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>56200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>37600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>118400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>194100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>14400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>10700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2795,56 +2992,62 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>920600</v>
+        <v>846400</v>
       </c>
       <c r="E46" s="3">
-        <v>995300</v>
+        <v>881200</v>
       </c>
       <c r="F46" s="3">
-        <v>1007900</v>
+        <v>914900</v>
       </c>
       <c r="G46" s="3">
-        <v>1017600</v>
+        <v>989100</v>
       </c>
       <c r="H46" s="3">
-        <v>1060500</v>
+        <v>1001700</v>
       </c>
       <c r="I46" s="3">
+        <v>1011300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1053900</v>
+      </c>
+      <c r="K46" s="3">
         <v>999600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1124800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1150800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1183400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1096600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1206600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>517800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>536200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2857,49 +3060,55 @@
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4200</v>
+        <v>7100</v>
       </c>
       <c r="E47" s="3">
-        <v>4200</v>
+        <v>6200</v>
       </c>
       <c r="F47" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>1700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2600</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2800</v>
       </c>
       <c r="N47" s="3">
         <v>2800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P47" s="3">
+        <v>2800</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -2919,56 +3128,62 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7700</v>
       </c>
-      <c r="E48" s="3">
-        <v>12700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>14100</v>
-      </c>
       <c r="G48" s="3">
-        <v>14900</v>
+        <v>12600</v>
       </c>
       <c r="H48" s="3">
-        <v>16300</v>
+        <v>14000</v>
       </c>
       <c r="I48" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K48" s="3">
         <v>18200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>18800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>12900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>12300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2981,56 +3196,62 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44100</v>
+        <v>42600</v>
       </c>
       <c r="E49" s="3">
-        <v>44900</v>
+        <v>43300</v>
       </c>
       <c r="F49" s="3">
-        <v>28200</v>
+        <v>43900</v>
       </c>
       <c r="G49" s="3">
-        <v>28700</v>
+        <v>44600</v>
       </c>
       <c r="H49" s="3">
-        <v>29500</v>
+        <v>28000</v>
       </c>
       <c r="I49" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K49" s="3">
         <v>18300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>19000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>19600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>15600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3043,8 +3264,14 @@
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3332,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,56 +3400,62 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3100</v>
-      </c>
       <c r="G52" s="3">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="H52" s="3">
         <v>3100</v>
       </c>
       <c r="I52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K52" s="3">
         <v>125100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>24800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>106400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>24300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3229,8 +3468,14 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3536,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>979800</v>
+        <v>902900</v>
       </c>
       <c r="E54" s="3">
-        <v>1061200</v>
+        <v>938800</v>
       </c>
       <c r="F54" s="3">
-        <v>1057500</v>
+        <v>973800</v>
       </c>
       <c r="G54" s="3">
-        <v>1064400</v>
+        <v>1054700</v>
       </c>
       <c r="H54" s="3">
-        <v>1109300</v>
+        <v>1051000</v>
       </c>
       <c r="I54" s="3">
+        <v>1057800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1102500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1162900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1168500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1215800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1241800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1221100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1249000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>523600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>542800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3353,8 +3604,14 @@
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3634,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3660,58 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>132600</v>
+        <v>141500</v>
       </c>
       <c r="E57" s="3">
-        <v>158000</v>
+        <v>143500</v>
       </c>
       <c r="F57" s="3">
-        <v>139200</v>
+        <v>131800</v>
       </c>
       <c r="G57" s="3">
-        <v>127400</v>
+        <v>157000</v>
       </c>
       <c r="H57" s="3">
-        <v>128300</v>
+        <v>138400</v>
       </c>
       <c r="I57" s="3">
+        <v>126600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>127500</v>
+      </c>
+      <c r="K57" s="3">
         <v>168700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>142300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>141700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>114800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>107200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>86400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>69900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>57700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3463,8 +3724,14 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3519,62 +3786,68 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>133100</v>
+        <v>119900</v>
       </c>
       <c r="E59" s="3">
-        <v>132600</v>
+        <v>125300</v>
       </c>
       <c r="F59" s="3">
-        <v>130600</v>
+        <v>132300</v>
       </c>
       <c r="G59" s="3">
-        <v>126300</v>
+        <v>131800</v>
       </c>
       <c r="H59" s="3">
-        <v>138200</v>
+        <v>129800</v>
       </c>
       <c r="I59" s="3">
+        <v>125500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>137400</v>
+      </c>
+      <c r="K59" s="3">
         <v>125400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>118200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>120300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>113100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>95100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>90900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>71400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>67400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3587,56 +3860,62 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>265700</v>
+        <v>261400</v>
       </c>
       <c r="E60" s="3">
-        <v>290600</v>
+        <v>268800</v>
       </c>
       <c r="F60" s="3">
-        <v>269900</v>
+        <v>264100</v>
       </c>
       <c r="G60" s="3">
-        <v>253700</v>
+        <v>288800</v>
       </c>
       <c r="H60" s="3">
-        <v>266600</v>
+        <v>268200</v>
       </c>
       <c r="I60" s="3">
+        <v>252100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>264900</v>
+      </c>
+      <c r="K60" s="3">
         <v>294100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>260500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>262000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>227900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>202300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>177200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>141200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>125100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3649,8 +3928,14 @@
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3711,56 +3996,62 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>21500</v>
+        <v>18800</v>
       </c>
       <c r="E62" s="3">
-        <v>27500</v>
+        <v>20500</v>
       </c>
       <c r="F62" s="3">
-        <v>18600</v>
+        <v>21400</v>
       </c>
       <c r="G62" s="3">
-        <v>19100</v>
+        <v>27300</v>
       </c>
       <c r="H62" s="3">
-        <v>20100</v>
+        <v>18500</v>
       </c>
       <c r="I62" s="3">
+        <v>18900</v>
+      </c>
+      <c r="J62" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K62" s="3">
         <v>22800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>23600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>16800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>7500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>7100</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3773,8 +4064,14 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +4132,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4200,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,56 +4268,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>299500</v>
+        <v>295900</v>
       </c>
       <c r="E66" s="3">
-        <v>328400</v>
+        <v>303300</v>
       </c>
       <c r="F66" s="3">
-        <v>295700</v>
+        <v>297600</v>
       </c>
       <c r="G66" s="3">
-        <v>278400</v>
+        <v>326400</v>
       </c>
       <c r="H66" s="3">
-        <v>291000</v>
+        <v>293900</v>
       </c>
       <c r="I66" s="3">
+        <v>276700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>289200</v>
+      </c>
+      <c r="K66" s="3">
         <v>319100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>285700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>286400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>245200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>209800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>184300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>141200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>125200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4021,8 +4336,14 @@
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4366,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4430,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4498,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,31 +4543,37 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1098500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>1127600</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V70" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4634,62 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>-1202800</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="3">
-        <v>-1093000</v>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I72" s="3">
+        <v>-1086200</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-867300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-688800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-694400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4355,8 +4702,14 @@
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4770,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4838,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4906,62 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>680400</v>
+        <v>607000</v>
       </c>
       <c r="E76" s="3">
-        <v>732800</v>
+        <v>635500</v>
       </c>
       <c r="F76" s="3">
-        <v>761800</v>
+        <v>676200</v>
       </c>
       <c r="G76" s="3">
-        <v>786000</v>
+        <v>728300</v>
       </c>
       <c r="H76" s="3">
-        <v>818300</v>
+        <v>757100</v>
       </c>
       <c r="I76" s="3">
+        <v>781100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>813200</v>
+      </c>
+      <c r="K76" s="3">
         <v>843800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>882700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>929400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>996600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1011300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1064700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-716100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-709900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4603,8 +4974,14 @@
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +5042,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="G81" s="3">
         <v>-38700</v>
       </c>
-      <c r="E81" s="3">
-        <v>-38900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-25200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-25000</v>
-      </c>
       <c r="H81" s="3">
-        <v>-41700</v>
+        <v>-25100</v>
       </c>
       <c r="I81" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-67700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-85400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-52900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-38400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-45600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-71100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-36200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-42500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-57900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-62300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5213,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4865,11 +5262,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
@@ -4880,8 +5277,14 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5345,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5413,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5481,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5549,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,8 +5617,14 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5237,11 +5670,11 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
@@ -5252,8 +5685,14 @@
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,8 +5715,10 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5323,11 +5764,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -5338,8 +5779,14 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5847,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,8 +5915,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5509,11 +5968,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
@@ -5524,8 +5983,14 @@
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +6013,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +6077,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +6145,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +6213,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,8 +6281,14 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5843,11 +6334,11 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
@@ -5858,8 +6349,14 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5905,11 +6402,11 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
@@ -5920,8 +6417,14 @@
       <c r="V101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5967,11 +6470,11 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
@@ -5980,6 +6483,12 @@
         <v>4</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>132800</v>
+        <v>131600</v>
       </c>
       <c r="E8" s="3">
-        <v>157300</v>
+        <v>135500</v>
       </c>
       <c r="F8" s="3">
-        <v>141200</v>
+        <v>160500</v>
       </c>
       <c r="G8" s="3">
-        <v>144300</v>
+        <v>144100</v>
       </c>
       <c r="H8" s="3">
-        <v>137400</v>
+        <v>147200</v>
       </c>
       <c r="I8" s="3">
-        <v>153900</v>
+        <v>140200</v>
       </c>
       <c r="J8" s="3">
+        <v>157100</v>
+      </c>
+      <c r="K8" s="3">
         <v>126000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>103300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>117100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>90700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>72400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>55900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>57700</v>
+        <v>53200</v>
       </c>
       <c r="E9" s="3">
-        <v>64300</v>
+        <v>58800</v>
       </c>
       <c r="F9" s="3">
-        <v>65400</v>
+        <v>65600</v>
       </c>
       <c r="G9" s="3">
-        <v>66600</v>
+        <v>66800</v>
       </c>
       <c r="H9" s="3">
-        <v>66600</v>
+        <v>68000</v>
       </c>
       <c r="I9" s="3">
-        <v>67100</v>
+        <v>68000</v>
       </c>
       <c r="J9" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K9" s="3">
         <v>64600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>60700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>56700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>74500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>56700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>47500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>75100</v>
+        <v>78500</v>
       </c>
       <c r="E10" s="3">
-        <v>93000</v>
+        <v>76600</v>
       </c>
       <c r="F10" s="3">
-        <v>75800</v>
+        <v>94900</v>
       </c>
       <c r="G10" s="3">
-        <v>77700</v>
+        <v>77300</v>
       </c>
       <c r="H10" s="3">
-        <v>70800</v>
+        <v>79200</v>
       </c>
       <c r="I10" s="3">
-        <v>86800</v>
+        <v>72200</v>
       </c>
       <c r="J10" s="3">
+        <v>88600</v>
+      </c>
+      <c r="K10" s="3">
         <v>61400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>55600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>53500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-1300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>27300</v>
+        <v>29500</v>
       </c>
       <c r="E12" s="3">
-        <v>32100</v>
+        <v>27800</v>
       </c>
       <c r="F12" s="3">
-        <v>34500</v>
+        <v>32800</v>
       </c>
       <c r="G12" s="3">
-        <v>32600</v>
+        <v>35200</v>
       </c>
       <c r="H12" s="3">
-        <v>25300</v>
+        <v>33300</v>
       </c>
       <c r="I12" s="3">
-        <v>29400</v>
+        <v>25800</v>
       </c>
       <c r="J12" s="3">
+        <v>30000</v>
+      </c>
+      <c r="K12" s="3">
         <v>22200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12900</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1186,14 +1206,17 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1254,14 +1277,17 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>163800</v>
+        <v>157600</v>
       </c>
       <c r="E17" s="3">
-        <v>181900</v>
+        <v>167100</v>
       </c>
       <c r="F17" s="3">
-        <v>189600</v>
+        <v>185600</v>
       </c>
       <c r="G17" s="3">
-        <v>189500</v>
+        <v>193500</v>
       </c>
       <c r="H17" s="3">
-        <v>167300</v>
+        <v>193300</v>
       </c>
       <c r="I17" s="3">
-        <v>183800</v>
+        <v>170700</v>
       </c>
       <c r="J17" s="3">
+        <v>187500</v>
+      </c>
+      <c r="K17" s="3">
         <v>164500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>193400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>192500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>162900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>140600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>117900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>86900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>74900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>61700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>77200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-31000</v>
+        <v>-25900</v>
       </c>
       <c r="E18" s="3">
-        <v>-24600</v>
+        <v>-31700</v>
       </c>
       <c r="F18" s="3">
-        <v>-48400</v>
+        <v>-25100</v>
       </c>
       <c r="G18" s="3">
-        <v>-45200</v>
+        <v>-49400</v>
       </c>
       <c r="H18" s="3">
-        <v>-29900</v>
+        <v>-46100</v>
       </c>
       <c r="I18" s="3">
-        <v>-29900</v>
+        <v>-30600</v>
       </c>
       <c r="J18" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-38500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-90100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-51800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-45800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-49800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-33300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-42700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,76 +1478,80 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8300</v>
+        <v>13600</v>
       </c>
       <c r="E20" s="3">
-        <v>11000</v>
+        <v>8500</v>
       </c>
       <c r="F20" s="3">
-        <v>9900</v>
+        <v>11300</v>
       </c>
       <c r="G20" s="3">
-        <v>7000</v>
+        <v>10100</v>
       </c>
       <c r="H20" s="3">
-        <v>5900</v>
+        <v>7100</v>
       </c>
       <c r="I20" s="3">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,32 +1594,35 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-9700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-13800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-34200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1643,150 +1683,159 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22700</v>
+        <v>-12400</v>
       </c>
       <c r="E23" s="3">
-        <v>-13600</v>
+        <v>-23200</v>
       </c>
       <c r="F23" s="3">
-        <v>-38500</v>
+        <v>-13800</v>
       </c>
       <c r="G23" s="3">
-        <v>-38200</v>
+        <v>-39300</v>
       </c>
       <c r="H23" s="3">
-        <v>-24100</v>
+        <v>-39000</v>
       </c>
       <c r="I23" s="3">
-        <v>-24400</v>
+        <v>-24600</v>
       </c>
       <c r="J23" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-40700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-66800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-85100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-52500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-38300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-45400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-31700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-43900</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>400</v>
       </c>
       <c r="J24" s="3">
         <v>400</v>
       </c>
       <c r="K24" s="3">
+        <v>400</v>
+      </c>
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-22900</v>
+        <v>-11400</v>
       </c>
       <c r="E26" s="3">
-        <v>-14200</v>
+        <v>-23400</v>
       </c>
       <c r="F26" s="3">
-        <v>-38500</v>
+        <v>-14500</v>
       </c>
       <c r="G26" s="3">
-        <v>-38600</v>
+        <v>-39200</v>
       </c>
       <c r="H26" s="3">
-        <v>-24700</v>
+        <v>-39300</v>
       </c>
       <c r="I26" s="3">
-        <v>-24800</v>
+        <v>-25200</v>
       </c>
       <c r="J26" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-41100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-85400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-38400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-37300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-22800</v>
+        <v>-11700</v>
       </c>
       <c r="E27" s="3">
-        <v>-14300</v>
+        <v>-23200</v>
       </c>
       <c r="F27" s="3">
-        <v>-38500</v>
+        <v>-14600</v>
       </c>
       <c r="G27" s="3">
-        <v>-38700</v>
+        <v>-39300</v>
       </c>
       <c r="H27" s="3">
-        <v>-25100</v>
+        <v>-39500</v>
       </c>
       <c r="I27" s="3">
-        <v>-24800</v>
+        <v>-25600</v>
       </c>
       <c r="J27" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-41500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-67700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-85400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-38400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-41300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-42500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-57900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-62300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2119,14 +2180,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8300</v>
+        <v>-13600</v>
       </c>
       <c r="E32" s="3">
-        <v>-11000</v>
+        <v>-8500</v>
       </c>
       <c r="F32" s="3">
-        <v>-9900</v>
+        <v>-11300</v>
       </c>
       <c r="G32" s="3">
-        <v>-7000</v>
+        <v>-10100</v>
       </c>
       <c r="H32" s="3">
-        <v>-5900</v>
+        <v>-7100</v>
       </c>
       <c r="I32" s="3">
-        <v>-5500</v>
+        <v>-6000</v>
       </c>
       <c r="J32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K32" s="3">
         <v>2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-22800</v>
+        <v>-11700</v>
       </c>
       <c r="E33" s="3">
-        <v>-14300</v>
+        <v>-23200</v>
       </c>
       <c r="F33" s="3">
-        <v>-38500</v>
+        <v>-14600</v>
       </c>
       <c r="G33" s="3">
-        <v>-38700</v>
+        <v>-39300</v>
       </c>
       <c r="H33" s="3">
-        <v>-25100</v>
+        <v>-39500</v>
       </c>
       <c r="I33" s="3">
-        <v>-24800</v>
+        <v>-25600</v>
       </c>
       <c r="J33" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-41500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-67700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-85400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-41300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-42500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-57900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-62300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-22800</v>
+        <v>-11700</v>
       </c>
       <c r="E35" s="3">
-        <v>-14300</v>
+        <v>-23200</v>
       </c>
       <c r="F35" s="3">
-        <v>-38500</v>
+        <v>-14600</v>
       </c>
       <c r="G35" s="3">
-        <v>-38700</v>
+        <v>-39300</v>
       </c>
       <c r="H35" s="3">
-        <v>-25100</v>
+        <v>-39500</v>
       </c>
       <c r="I35" s="3">
-        <v>-24800</v>
+        <v>-25600</v>
       </c>
       <c r="J35" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-41500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-67700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-85400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-41300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-42500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-57900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-62300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2744,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>303200</v>
+        <v>445400</v>
       </c>
       <c r="E41" s="3">
-        <v>291100</v>
+        <v>309400</v>
       </c>
       <c r="F41" s="3">
-        <v>432900</v>
+        <v>297000</v>
       </c>
       <c r="G41" s="3">
-        <v>557300</v>
+        <v>441700</v>
       </c>
       <c r="H41" s="3">
-        <v>576400</v>
+        <v>568700</v>
       </c>
       <c r="I41" s="3">
-        <v>625300</v>
+        <v>588200</v>
       </c>
       <c r="J41" s="3">
+        <v>638100</v>
+      </c>
+      <c r="K41" s="3">
         <v>469400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>312700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>332700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>297900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>208600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>125700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>862500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>133300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>96800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2726,59 +2813,62 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>417600</v>
+        <v>260900</v>
       </c>
       <c r="E42" s="3">
-        <v>463700</v>
+        <v>426100</v>
       </c>
       <c r="F42" s="3">
-        <v>348300</v>
+        <v>473200</v>
       </c>
       <c r="G42" s="3">
-        <v>293600</v>
+        <v>355400</v>
       </c>
       <c r="H42" s="3">
-        <v>288200</v>
+        <v>299600</v>
       </c>
       <c r="I42" s="3">
-        <v>239800</v>
+        <v>294000</v>
       </c>
       <c r="J42" s="3">
+        <v>244700</v>
+      </c>
+      <c r="K42" s="3">
         <v>445800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>500500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>617700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>698000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>754400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>691000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>257100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>297700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>374700</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2794,59 +2884,62 @@
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>92500</v>
+        <v>80900</v>
       </c>
       <c r="E43" s="3">
         <v>94400</v>
       </c>
       <c r="F43" s="3">
-        <v>88000</v>
+        <v>96300</v>
       </c>
       <c r="G43" s="3">
-        <v>105200</v>
+        <v>89800</v>
       </c>
       <c r="H43" s="3">
-        <v>107400</v>
+        <v>107300</v>
       </c>
       <c r="I43" s="3">
-        <v>118700</v>
+        <v>109600</v>
       </c>
       <c r="J43" s="3">
+        <v>121100</v>
+      </c>
+      <c r="K43" s="3">
         <v>106800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>121100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>118200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>117300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>102000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>85700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>72500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>76100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2924,65 +3020,68 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
+      <c r="W44" s="3">
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33100</v>
+        <v>35700</v>
       </c>
       <c r="E45" s="3">
-        <v>32100</v>
+        <v>33800</v>
       </c>
       <c r="F45" s="3">
-        <v>45700</v>
+        <v>32700</v>
       </c>
       <c r="G45" s="3">
-        <v>33100</v>
+        <v>46600</v>
       </c>
       <c r="H45" s="3">
-        <v>29700</v>
+        <v>33800</v>
       </c>
       <c r="I45" s="3">
-        <v>27500</v>
+        <v>30300</v>
       </c>
       <c r="J45" s="3">
+        <v>28100</v>
+      </c>
+      <c r="K45" s="3">
         <v>31900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>65200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>118400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>194100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2998,59 +3097,62 @@
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>846400</v>
+        <v>822900</v>
       </c>
       <c r="E46" s="3">
-        <v>881200</v>
+        <v>863700</v>
       </c>
       <c r="F46" s="3">
-        <v>914900</v>
+        <v>899200</v>
       </c>
       <c r="G46" s="3">
-        <v>989100</v>
+        <v>933600</v>
       </c>
       <c r="H46" s="3">
-        <v>1001700</v>
+        <v>1009300</v>
       </c>
       <c r="I46" s="3">
-        <v>1011300</v>
+        <v>1022100</v>
       </c>
       <c r="J46" s="3">
+        <v>1031900</v>
+      </c>
+      <c r="K46" s="3">
         <v>1053900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>999600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1124800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1150800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1183400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1096600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1206600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>517800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>536200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3066,43 +3168,46 @@
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="E47" s="3">
-        <v>6200</v>
+        <v>7200</v>
       </c>
       <c r="F47" s="3">
-        <v>4100</v>
+        <v>6300</v>
       </c>
       <c r="G47" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="H47" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>1700</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2600</v>
       </c>
       <c r="M47" s="3">
         <v>2600</v>
       </c>
       <c r="N47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="O47" s="3">
         <v>2800</v>
@@ -3110,8 +3215,8 @@
       <c r="P47" s="3">
         <v>2800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>2800</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
@@ -3134,59 +3239,62 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5800</v>
+        <v>4500</v>
       </c>
       <c r="E48" s="3">
-        <v>7100</v>
+        <v>5900</v>
       </c>
       <c r="F48" s="3">
-        <v>7700</v>
+        <v>7200</v>
       </c>
       <c r="G48" s="3">
-        <v>12600</v>
+        <v>7800</v>
       </c>
       <c r="H48" s="3">
-        <v>14000</v>
+        <v>12900</v>
       </c>
       <c r="I48" s="3">
-        <v>14800</v>
+        <v>14300</v>
       </c>
       <c r="J48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K48" s="3">
         <v>16200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3202,59 +3310,62 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>42600</v>
+        <v>26500</v>
       </c>
       <c r="E49" s="3">
-        <v>43300</v>
+        <v>43400</v>
       </c>
       <c r="F49" s="3">
-        <v>43900</v>
+        <v>44200</v>
       </c>
       <c r="G49" s="3">
-        <v>44600</v>
+        <v>44800</v>
       </c>
       <c r="H49" s="3">
-        <v>28000</v>
+        <v>45500</v>
       </c>
       <c r="I49" s="3">
-        <v>28500</v>
+        <v>28600</v>
       </c>
       <c r="J49" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K49" s="3">
         <v>29300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3523,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>1100</v>
       </c>
       <c r="F52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="I52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>125100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>106400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3665,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>902900</v>
+        <v>861100</v>
       </c>
       <c r="E54" s="3">
-        <v>938800</v>
+        <v>921400</v>
       </c>
       <c r="F54" s="3">
-        <v>973800</v>
+        <v>958000</v>
       </c>
       <c r="G54" s="3">
-        <v>1054700</v>
+        <v>993700</v>
       </c>
       <c r="H54" s="3">
-        <v>1051000</v>
+        <v>1076200</v>
       </c>
       <c r="I54" s="3">
-        <v>1057800</v>
+        <v>1072400</v>
       </c>
       <c r="J54" s="3">
+        <v>1079400</v>
+      </c>
+      <c r="K54" s="3">
         <v>1102500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1162900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1168500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1215800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1241800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1221100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1249000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>523600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>542800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3792,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>141500</v>
+        <v>128700</v>
       </c>
       <c r="E57" s="3">
-        <v>143500</v>
+        <v>144400</v>
       </c>
       <c r="F57" s="3">
-        <v>131800</v>
+        <v>146400</v>
       </c>
       <c r="G57" s="3">
-        <v>157000</v>
+        <v>134500</v>
       </c>
       <c r="H57" s="3">
-        <v>138400</v>
+        <v>160300</v>
       </c>
       <c r="I57" s="3">
-        <v>126600</v>
+        <v>141200</v>
       </c>
       <c r="J57" s="3">
+        <v>129200</v>
+      </c>
+      <c r="K57" s="3">
         <v>127500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>168700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>142300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>141700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>114800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>107200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>86400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>69900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>57700</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3730,31 +3861,34 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>7300</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3792,65 +3926,68 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>119900</v>
+        <v>100800</v>
       </c>
       <c r="E59" s="3">
-        <v>125300</v>
+        <v>122300</v>
       </c>
       <c r="F59" s="3">
-        <v>132300</v>
+        <v>127900</v>
       </c>
       <c r="G59" s="3">
-        <v>131800</v>
+        <v>135000</v>
       </c>
       <c r="H59" s="3">
-        <v>129800</v>
+        <v>134500</v>
       </c>
       <c r="I59" s="3">
-        <v>125500</v>
+        <v>132500</v>
       </c>
       <c r="J59" s="3">
+        <v>128100</v>
+      </c>
+      <c r="K59" s="3">
         <v>137400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>125400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>118200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>120300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>113100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>90900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>71400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,59 +4003,62 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>261400</v>
+        <v>236800</v>
       </c>
       <c r="E60" s="3">
-        <v>268800</v>
+        <v>266700</v>
       </c>
       <c r="F60" s="3">
-        <v>264100</v>
+        <v>274300</v>
       </c>
       <c r="G60" s="3">
-        <v>288800</v>
+        <v>269500</v>
       </c>
       <c r="H60" s="3">
-        <v>268200</v>
+        <v>294700</v>
       </c>
       <c r="I60" s="3">
-        <v>252100</v>
+        <v>273700</v>
       </c>
       <c r="J60" s="3">
+        <v>257300</v>
+      </c>
+      <c r="K60" s="3">
         <v>264900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>294100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>260500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>262000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>227900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>202300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>177200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>141200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>125100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3934,8 +4074,11 @@
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,59 +4145,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18800</v>
+        <v>4000</v>
       </c>
       <c r="E62" s="3">
-        <v>20500</v>
+        <v>19200</v>
       </c>
       <c r="F62" s="3">
-        <v>21400</v>
+        <v>20900</v>
       </c>
       <c r="G62" s="3">
-        <v>27300</v>
+        <v>21800</v>
       </c>
       <c r="H62" s="3">
-        <v>18500</v>
+        <v>27900</v>
       </c>
       <c r="I62" s="3">
         <v>18900</v>
       </c>
       <c r="J62" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K62" s="3">
         <v>20000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7100</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4429,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>295900</v>
+        <v>253200</v>
       </c>
       <c r="E66" s="3">
-        <v>303300</v>
+        <v>302000</v>
       </c>
       <c r="F66" s="3">
-        <v>297600</v>
+        <v>309500</v>
       </c>
       <c r="G66" s="3">
-        <v>326400</v>
+        <v>303700</v>
       </c>
       <c r="H66" s="3">
-        <v>293900</v>
+        <v>333000</v>
       </c>
       <c r="I66" s="3">
-        <v>276700</v>
+        <v>299900</v>
       </c>
       <c r="J66" s="3">
+        <v>282300</v>
+      </c>
+      <c r="K66" s="3">
         <v>289200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>319100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>285700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>286400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>245200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>209800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>184300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>141200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>125200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,14 +4717,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>1098500</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1127600</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4566,14 +4734,17 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-      <c r="W70" s="3" t="s">
-        <v>4</v>
+      <c r="W70" s="3">
+        <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,19 +4811,22 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
-        <v>-1202800</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-1227300</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
@@ -4660,39 +4834,39 @@
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3">
-        <v>-1086200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-1108400</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-867300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-688800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-694400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5095,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>607000</v>
+        <v>607900</v>
       </c>
       <c r="E76" s="3">
-        <v>635500</v>
+        <v>619400</v>
       </c>
       <c r="F76" s="3">
-        <v>676200</v>
+        <v>648500</v>
       </c>
       <c r="G76" s="3">
-        <v>728300</v>
+        <v>690000</v>
       </c>
       <c r="H76" s="3">
-        <v>757100</v>
+        <v>743200</v>
       </c>
       <c r="I76" s="3">
-        <v>781100</v>
+        <v>772600</v>
       </c>
       <c r="J76" s="3">
+        <v>797100</v>
+      </c>
+      <c r="K76" s="3">
         <v>813200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>843800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>882700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>929400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>996600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1011300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1064700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-716100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-709900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-22800</v>
+        <v>-11700</v>
       </c>
       <c r="E81" s="3">
-        <v>-14300</v>
+        <v>-23200</v>
       </c>
       <c r="F81" s="3">
-        <v>-38500</v>
+        <v>-14600</v>
       </c>
       <c r="G81" s="3">
-        <v>-38700</v>
+        <v>-39300</v>
       </c>
       <c r="H81" s="3">
-        <v>-25100</v>
+        <v>-39500</v>
       </c>
       <c r="I81" s="3">
-        <v>-24800</v>
+        <v>-25600</v>
       </c>
       <c r="J81" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-41500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-67700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-85400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-41300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-42500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-57900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-62300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5268,8 +5467,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>4</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,8 +5837,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5676,8 +5893,8 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5770,8 +5991,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6148,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5974,8 +6204,8 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,8 +6530,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6340,8 +6586,8 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6408,8 +6657,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
@@ -6423,8 +6672,11 @@
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6476,8 +6728,8 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
@@ -6489,6 +6741,9 @@
         <v>4</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>131600</v>
+        <v>120500</v>
       </c>
       <c r="E8" s="3">
-        <v>135500</v>
+        <v>128500</v>
       </c>
       <c r="F8" s="3">
+        <v>133100</v>
+      </c>
+      <c r="G8" s="3">
         <v>160500</v>
       </c>
-      <c r="G8" s="3">
-        <v>144100</v>
-      </c>
       <c r="H8" s="3">
-        <v>147200</v>
+        <v>140100</v>
       </c>
       <c r="I8" s="3">
-        <v>140200</v>
+        <v>144000</v>
       </c>
       <c r="J8" s="3">
+        <v>144700</v>
+      </c>
+      <c r="K8" s="3">
         <v>157100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>126000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>116200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>103300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>140700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>117100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>90700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>68700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>72400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>55900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27100</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>53200</v>
+        <v>43500</v>
       </c>
       <c r="E9" s="3">
-        <v>58800</v>
+        <v>51900</v>
       </c>
       <c r="F9" s="3">
+        <v>57800</v>
+      </c>
+      <c r="G9" s="3">
         <v>65600</v>
       </c>
-      <c r="G9" s="3">
-        <v>66800</v>
-      </c>
       <c r="H9" s="3">
-        <v>68000</v>
+        <v>64900</v>
       </c>
       <c r="I9" s="3">
-        <v>68000</v>
+        <v>66500</v>
       </c>
       <c r="J9" s="3">
+        <v>70200</v>
+      </c>
+      <c r="K9" s="3">
         <v>68400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>64600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>60700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>56700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>74500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>56700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>37200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>78500</v>
+        <v>77000</v>
       </c>
       <c r="E10" s="3">
         <v>76600</v>
       </c>
       <c r="F10" s="3">
+        <v>75300</v>
+      </c>
+      <c r="G10" s="3">
         <v>94900</v>
       </c>
-      <c r="G10" s="3">
-        <v>77300</v>
-      </c>
       <c r="H10" s="3">
-        <v>79200</v>
+        <v>75200</v>
       </c>
       <c r="I10" s="3">
-        <v>72200</v>
+        <v>77500</v>
       </c>
       <c r="J10" s="3">
+        <v>74600</v>
+      </c>
+      <c r="K10" s="3">
         <v>88600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>55600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>53500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>39200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>29500</v>
+        <v>25600</v>
       </c>
       <c r="E12" s="3">
-        <v>27800</v>
+        <v>28800</v>
       </c>
       <c r="F12" s="3">
+        <v>27300</v>
+      </c>
+      <c r="G12" s="3">
         <v>32800</v>
       </c>
-      <c r="G12" s="3">
-        <v>35200</v>
-      </c>
       <c r="H12" s="3">
-        <v>33300</v>
+        <v>34200</v>
       </c>
       <c r="I12" s="3">
-        <v>25800</v>
+        <v>32600</v>
       </c>
       <c r="J12" s="3">
+        <v>26600</v>
+      </c>
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12900</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,31 +1161,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1209,37 +1229,40 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1280,14 +1303,17 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>157600</v>
+        <v>132500</v>
       </c>
       <c r="E17" s="3">
-        <v>167100</v>
+        <v>153800</v>
       </c>
       <c r="F17" s="3">
-        <v>185600</v>
+        <v>164200</v>
       </c>
       <c r="G17" s="3">
-        <v>193500</v>
+        <v>185700</v>
       </c>
       <c r="H17" s="3">
-        <v>193300</v>
+        <v>188100</v>
       </c>
       <c r="I17" s="3">
-        <v>170700</v>
+        <v>189100</v>
       </c>
       <c r="J17" s="3">
+        <v>176300</v>
+      </c>
+      <c r="K17" s="3">
         <v>187500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>164500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>180300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>193400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>192500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>162900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>140600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>117900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>86900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>74900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>77200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-25900</v>
+        <v>-12000</v>
       </c>
       <c r="E18" s="3">
-        <v>-31700</v>
+        <v>-25300</v>
       </c>
       <c r="F18" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-25100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-49400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-46100</v>
+        <v>-48000</v>
       </c>
       <c r="I18" s="3">
-        <v>-30600</v>
+        <v>-45100</v>
       </c>
       <c r="J18" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-30500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-90100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-51800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-45800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-49800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-49200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-33300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-42700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,102 +1512,106 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>13600</v>
+        <v>-4200</v>
       </c>
       <c r="E20" s="3">
-        <v>8500</v>
+        <v>-6600</v>
       </c>
       <c r="F20" s="3">
-        <v>11300</v>
+        <v>-1700</v>
       </c>
       <c r="G20" s="3">
-        <v>10100</v>
+        <v>-4100</v>
       </c>
       <c r="H20" s="3">
-        <v>7100</v>
+        <v>-2700</v>
       </c>
       <c r="I20" s="3">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>5600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-31100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1597,55 +1634,58 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-9700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-13800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>-34200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1686,156 +1726,165 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-12400</v>
+        <v>-1400</v>
       </c>
       <c r="E23" s="3">
-        <v>-23200</v>
+        <v>-12100</v>
       </c>
       <c r="F23" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="G23" s="3">
         <v>-13800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H23" s="3">
-        <v>-39000</v>
+        <v>-38200</v>
       </c>
       <c r="I23" s="3">
-        <v>-24600</v>
+        <v>-38200</v>
       </c>
       <c r="J23" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-24900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-40700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-66800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-85100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-37300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-43900</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
       </c>
       <c r="L24" s="3">
+        <v>400</v>
+      </c>
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-11400</v>
+        <v>-1300</v>
       </c>
       <c r="E26" s="3">
-        <v>-23400</v>
+        <v>-11100</v>
       </c>
       <c r="F26" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-14500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-39200</v>
-      </c>
       <c r="H26" s="3">
-        <v>-39300</v>
+        <v>-38200</v>
       </c>
       <c r="I26" s="3">
-        <v>-25200</v>
+        <v>-38500</v>
       </c>
       <c r="J26" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-25300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-85400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-38400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-46600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-37300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-11700</v>
+        <v>-1500</v>
       </c>
       <c r="E27" s="3">
-        <v>-23200</v>
+        <v>-11400</v>
       </c>
       <c r="F27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="G27" s="3">
         <v>-14600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H27" s="3">
-        <v>-39500</v>
+        <v>-38200</v>
       </c>
       <c r="I27" s="3">
-        <v>-25600</v>
+        <v>-38600</v>
       </c>
       <c r="J27" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-25300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-67700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-85400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-52900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-71100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-41300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-42500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-57900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-62300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2183,14 +2244,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>4</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13600</v>
+        <v>4200</v>
       </c>
       <c r="E32" s="3">
-        <v>-8500</v>
+        <v>6600</v>
       </c>
       <c r="F32" s="3">
-        <v>-11300</v>
+        <v>1700</v>
       </c>
       <c r="G32" s="3">
-        <v>-10100</v>
+        <v>4100</v>
       </c>
       <c r="H32" s="3">
-        <v>-7100</v>
+        <v>2700</v>
       </c>
       <c r="I32" s="3">
-        <v>-6000</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-11700</v>
+        <v>-1500</v>
       </c>
       <c r="E33" s="3">
-        <v>-23200</v>
+        <v>-11400</v>
       </c>
       <c r="F33" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="G33" s="3">
         <v>-14600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H33" s="3">
-        <v>-39500</v>
+        <v>-38200</v>
       </c>
       <c r="I33" s="3">
-        <v>-25600</v>
+        <v>-38600</v>
       </c>
       <c r="J33" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-25300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-67700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-85400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-52900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-71100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-41300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-42500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-57900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-62300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-11700</v>
+        <v>-1500</v>
       </c>
       <c r="E35" s="3">
-        <v>-23200</v>
+        <v>-11400</v>
       </c>
       <c r="F35" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="G35" s="3">
         <v>-14600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H35" s="3">
-        <v>-39500</v>
+        <v>-38200</v>
       </c>
       <c r="I35" s="3">
-        <v>-25600</v>
+        <v>-38600</v>
       </c>
       <c r="J35" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-25300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-67700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-85400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-52900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-71100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-41300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-42500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-57900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-62300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>445400</v>
+        <v>458200</v>
       </c>
       <c r="E41" s="3">
-        <v>309400</v>
+        <v>434800</v>
       </c>
       <c r="F41" s="3">
-        <v>297000</v>
+        <v>303900</v>
       </c>
       <c r="G41" s="3">
-        <v>441700</v>
+        <v>297100</v>
       </c>
       <c r="H41" s="3">
-        <v>568700</v>
+        <v>429400</v>
       </c>
       <c r="I41" s="3">
-        <v>588200</v>
+        <v>556200</v>
       </c>
       <c r="J41" s="3">
+        <v>607300</v>
+      </c>
+      <c r="K41" s="3">
         <v>638100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>469400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>312700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>332700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>297900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>208600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>125700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>862500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>133300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>96800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2816,62 +2903,65 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>260900</v>
+        <v>254100</v>
       </c>
       <c r="E42" s="3">
-        <v>426100</v>
+        <v>254600</v>
       </c>
       <c r="F42" s="3">
-        <v>473200</v>
+        <v>418600</v>
       </c>
       <c r="G42" s="3">
-        <v>355400</v>
+        <v>473300</v>
       </c>
       <c r="H42" s="3">
-        <v>299600</v>
+        <v>345500</v>
       </c>
       <c r="I42" s="3">
-        <v>294000</v>
+        <v>293000</v>
       </c>
       <c r="J42" s="3">
+        <v>303600</v>
+      </c>
+      <c r="K42" s="3">
         <v>244700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>445800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>500500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>617700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>698000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>754400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>691000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>257100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>297700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>374700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>80900</v>
+        <v>70400</v>
       </c>
       <c r="E43" s="3">
-        <v>94400</v>
+        <v>86500</v>
       </c>
       <c r="F43" s="3">
-        <v>96300</v>
+        <v>92700</v>
       </c>
       <c r="G43" s="3">
-        <v>89800</v>
+        <v>102500</v>
       </c>
       <c r="H43" s="3">
-        <v>107300</v>
+        <v>87300</v>
       </c>
       <c r="I43" s="3">
-        <v>109600</v>
+        <v>104900</v>
       </c>
       <c r="J43" s="3">
+        <v>113200</v>
+      </c>
+      <c r="K43" s="3">
         <v>121100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>106800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>118200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>117300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>102000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>85700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>72500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>76100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2958,31 +3051,34 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
+        <v>2600</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>3100</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3023,68 +3119,71 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>4</v>
+      <c r="X44" s="3">
+        <v>0</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>35700</v>
+        <v>29600</v>
       </c>
       <c r="E45" s="3">
-        <v>33800</v>
+        <v>7400</v>
       </c>
       <c r="F45" s="3">
-        <v>32700</v>
+        <v>33200</v>
       </c>
       <c r="G45" s="3">
-        <v>46600</v>
+        <v>10400</v>
       </c>
       <c r="H45" s="3">
-        <v>33800</v>
+        <v>45300</v>
       </c>
       <c r="I45" s="3">
-        <v>30300</v>
+        <v>33000</v>
       </c>
       <c r="J45" s="3">
+        <v>31300</v>
+      </c>
+      <c r="K45" s="3">
         <v>28100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>65200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>118400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>194100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3100,62 +3199,65 @@
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>822900</v>
+        <v>819700</v>
       </c>
       <c r="E46" s="3">
-        <v>863700</v>
+        <v>803200</v>
       </c>
       <c r="F46" s="3">
-        <v>899200</v>
+        <v>848400</v>
       </c>
       <c r="G46" s="3">
-        <v>933600</v>
+        <v>899400</v>
       </c>
       <c r="H46" s="3">
-        <v>1009300</v>
+        <v>907600</v>
       </c>
       <c r="I46" s="3">
-        <v>1022100</v>
+        <v>987200</v>
       </c>
       <c r="J46" s="3">
+        <v>1055500</v>
+      </c>
+      <c r="K46" s="3">
         <v>1031900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1053900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>999600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1124800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1150800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1183400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1096600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1206600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>517800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>536200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3171,46 +3273,49 @@
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="E47" s="3">
-        <v>7200</v>
+        <v>7000</v>
       </c>
       <c r="F47" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G47" s="3">
         <v>6300</v>
       </c>
-      <c r="G47" s="3">
-        <v>4200</v>
-      </c>
       <c r="H47" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="I47" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>1700</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2600</v>
       </c>
       <c r="N47" s="3">
         <v>2600</v>
       </c>
       <c r="O47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="P47" s="3">
         <v>2800</v>
@@ -3218,8 +3323,8 @@
       <c r="Q47" s="3">
         <v>2800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>2800</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -3242,62 +3347,65 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="E48" s="3">
-        <v>5900</v>
+        <v>4400</v>
       </c>
       <c r="F48" s="3">
+        <v>5800</v>
+      </c>
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="G48" s="3">
-        <v>7800</v>
-      </c>
       <c r="H48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>12600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="M48" s="3">
+        <v>18200</v>
+      </c>
+      <c r="N48" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O48" s="3">
+        <v>18800</v>
+      </c>
+      <c r="P48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>12900</v>
       </c>
-      <c r="I48" s="3">
-        <v>14300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>15100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>16200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>18200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>20000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>18800</v>
-      </c>
-      <c r="O48" s="3">
-        <v>15200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>12900</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3313,62 +3421,65 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>26500</v>
+        <v>26300</v>
       </c>
       <c r="E49" s="3">
-        <v>43400</v>
+        <v>25900</v>
       </c>
       <c r="F49" s="3">
+        <v>42700</v>
+      </c>
+      <c r="G49" s="3">
         <v>44200</v>
       </c>
-      <c r="G49" s="3">
-        <v>44800</v>
-      </c>
       <c r="H49" s="3">
-        <v>45500</v>
+        <v>43500</v>
       </c>
       <c r="I49" s="3">
-        <v>28600</v>
+        <v>44500</v>
       </c>
       <c r="J49" s="3">
+        <v>29600</v>
+      </c>
+      <c r="K49" s="3">
         <v>29100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3800</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3643,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3535,53 +3655,53 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>1100</v>
       </c>
       <c r="G52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="H52" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>125100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>106400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>861100</v>
+        <v>856600</v>
       </c>
       <c r="E54" s="3">
-        <v>921400</v>
+        <v>840600</v>
       </c>
       <c r="F54" s="3">
-        <v>958000</v>
+        <v>905100</v>
       </c>
       <c r="G54" s="3">
-        <v>993700</v>
+        <v>958300</v>
       </c>
       <c r="H54" s="3">
-        <v>1076200</v>
+        <v>966000</v>
       </c>
       <c r="I54" s="3">
-        <v>1072400</v>
+        <v>1052600</v>
       </c>
       <c r="J54" s="3">
+        <v>1107400</v>
+      </c>
+      <c r="K54" s="3">
         <v>1079400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1102500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1162900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1168500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1215800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1241800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1221100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1249000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>523600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>542800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>128700</v>
+        <v>128500</v>
       </c>
       <c r="E57" s="3">
-        <v>144400</v>
+        <v>127100</v>
       </c>
       <c r="F57" s="3">
-        <v>146400</v>
+        <v>143100</v>
       </c>
       <c r="G57" s="3">
-        <v>134500</v>
+        <v>150100</v>
       </c>
       <c r="H57" s="3">
-        <v>160300</v>
+        <v>132000</v>
       </c>
       <c r="I57" s="3">
-        <v>141200</v>
+        <v>159000</v>
       </c>
       <c r="J57" s="3">
+        <v>148800</v>
+      </c>
+      <c r="K57" s="3">
         <v>129200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>127500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>168700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>142300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>141700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>114800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>107200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>57700</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3864,34 +3995,37 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7300</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+        <v>9700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3929,68 +4063,71 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100800</v>
+        <v>63100</v>
       </c>
       <c r="E59" s="3">
-        <v>122300</v>
+        <v>55100</v>
       </c>
       <c r="F59" s="3">
-        <v>127900</v>
+        <v>68200</v>
       </c>
       <c r="G59" s="3">
-        <v>135000</v>
+        <v>61000</v>
       </c>
       <c r="H59" s="3">
-        <v>134500</v>
+        <v>84000</v>
       </c>
       <c r="I59" s="3">
-        <v>132500</v>
+        <v>87800</v>
       </c>
       <c r="J59" s="3">
+        <v>83500</v>
+      </c>
+      <c r="K59" s="3">
         <v>128100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>137400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>125400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>120300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>113100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>95100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>90900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4006,62 +4143,65 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>236800</v>
+        <v>233600</v>
       </c>
       <c r="E60" s="3">
-        <v>266700</v>
+        <v>231100</v>
       </c>
       <c r="F60" s="3">
-        <v>274300</v>
+        <v>262000</v>
       </c>
       <c r="G60" s="3">
-        <v>269500</v>
+        <v>274400</v>
       </c>
       <c r="H60" s="3">
-        <v>294700</v>
+        <v>262000</v>
       </c>
       <c r="I60" s="3">
-        <v>273700</v>
+        <v>288300</v>
       </c>
       <c r="J60" s="3">
+        <v>282600</v>
+      </c>
+      <c r="K60" s="3">
         <v>257300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>264900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>294100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>260500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>262000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>227900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>202300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>177200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>141200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>125100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4077,31 +4217,34 @@
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4148,62 +4291,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4000</v>
+        <v>2100</v>
       </c>
       <c r="E62" s="3">
-        <v>19200</v>
+        <v>2500</v>
       </c>
       <c r="F62" s="3">
-        <v>20900</v>
+        <v>15500</v>
       </c>
       <c r="G62" s="3">
-        <v>21800</v>
+        <v>17200</v>
       </c>
       <c r="H62" s="3">
-        <v>27900</v>
+        <v>17500</v>
       </c>
       <c r="I62" s="3">
-        <v>18900</v>
+        <v>21100</v>
       </c>
       <c r="J62" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K62" s="3">
         <v>19300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7100</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>253200</v>
+        <v>237200</v>
       </c>
       <c r="E66" s="3">
-        <v>302000</v>
+        <v>235000</v>
       </c>
       <c r="F66" s="3">
-        <v>309500</v>
+        <v>280800</v>
       </c>
       <c r="G66" s="3">
-        <v>303700</v>
+        <v>295300</v>
       </c>
       <c r="H66" s="3">
-        <v>333000</v>
+        <v>283200</v>
       </c>
       <c r="I66" s="3">
-        <v>299900</v>
+        <v>315500</v>
       </c>
       <c r="J66" s="3">
+        <v>302100</v>
+      </c>
+      <c r="K66" s="3">
         <v>282300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>289200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>319100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>285700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>286400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>245200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>209800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>184300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>141200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>125200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,14 +4888,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>1098500</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1127600</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4737,14 +4905,17 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-      <c r="X70" s="3" t="s">
-        <v>4</v>
+      <c r="X70" s="3">
+        <v>0</v>
       </c>
       <c r="Y70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1227300</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>-1232100</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-1228100</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="I72" s="3">
+        <v>-1147700</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1108400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-867300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3">
         <v>-688800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-694400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>607900</v>
+        <v>611500</v>
       </c>
       <c r="E76" s="3">
-        <v>619400</v>
+        <v>593400</v>
       </c>
       <c r="F76" s="3">
-        <v>648500</v>
+        <v>608500</v>
       </c>
       <c r="G76" s="3">
-        <v>690000</v>
+        <v>648700</v>
       </c>
       <c r="H76" s="3">
-        <v>743200</v>
+        <v>670700</v>
       </c>
       <c r="I76" s="3">
-        <v>772600</v>
+        <v>726900</v>
       </c>
       <c r="J76" s="3">
+        <v>797700</v>
+      </c>
+      <c r="K76" s="3">
         <v>797100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>813200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>843800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>882700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>929400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>996600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1011300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1064700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-716100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-709900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-11700</v>
+        <v>-1500</v>
       </c>
       <c r="E81" s="3">
-        <v>-23200</v>
+        <v>-11400</v>
       </c>
       <c r="F81" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="G81" s="3">
         <v>-14600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-39300</v>
-      </c>
       <c r="H81" s="3">
-        <v>-39500</v>
+        <v>-38200</v>
       </c>
       <c r="I81" s="3">
-        <v>-25600</v>
+        <v>-38600</v>
       </c>
       <c r="J81" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-25300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-67700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-85400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-52900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-71100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-41300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-42500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-57900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-62300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,31 +5612,32 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5470,8 +5669,8 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,31 +6054,34 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -5896,8 +6113,8 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,31 +6158,32 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5994,8 +6215,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,31 +6378,34 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6207,8 +6437,8 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,31 +6776,34 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -6589,8 +6835,8 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
@@ -6604,31 +6850,34 @@
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6660,8 +6909,8 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
@@ -6675,8 +6924,11 @@
       <c r="Y101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6731,8 +6983,8 @@
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
@@ -6744,6 +6996,9 @@
         <v>4</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E8" s="3">
         <v>120500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>128500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>133100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>160500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>144000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>144700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>157100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>126000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>116200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>103300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>140700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>117100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>90700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>68700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>72400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>55900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E9" s="3">
         <v>43500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>65600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>64900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>66500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>70200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>68400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>64600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>60700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>56700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>74500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>56700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>37200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E10" s="3">
         <v>77000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>76600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>94900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>75200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>61400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>53500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>39200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>46400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E12" s="3">
         <v>25600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12900</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1190,8 +1209,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1232,25 +1251,28 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>900</v>
       </c>
       <c r="G15" s="3">
         <v>900</v>
@@ -1259,14 +1281,14 @@
         <v>900</v>
       </c>
       <c r="I15" s="3">
+        <v>900</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1306,14 +1328,17 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E17" s="3">
         <v>132500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>164200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>185700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>188100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>189100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>176300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>187500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>164500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>180300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>193400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>192500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>162900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>117900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>86900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>74900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>61700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>77200</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-25300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-48000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-45100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-38500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-64000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-90100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-51800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-49800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-49200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-33300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-42700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,109 +1545,113 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-44400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-44500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1637,32 +1673,35 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-9700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>-34200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1687,8 +1726,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1729,162 +1768,171 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-38200</v>
       </c>
       <c r="I23" s="3">
         <v>-38200</v>
       </c>
       <c r="J23" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-25400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-40700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-66800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-85100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-52500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-45400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-46600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-31700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-37300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-43900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>400</v>
       </c>
       <c r="L24" s="3">
         <v>400</v>
       </c>
       <c r="M24" s="3">
+        <v>400</v>
+      </c>
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-67700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-85400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-52900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-45600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-46600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-31800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-37300</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-67700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-85400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-52900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-45600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-71100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-41300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-42500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-57900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-62300</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2247,14 +2307,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-67700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-85400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-52900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-45600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-71100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-41300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-42500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-57900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-62300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-67700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-85400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-52900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-45600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-71100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-41300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-42500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-57900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-62300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>547900</v>
+      </c>
+      <c r="E41" s="3">
         <v>458200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>434800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>303900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>297100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>429400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>556200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>607300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>638100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>469400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>312700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>332700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>297900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>208600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>125700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>862500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>133300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>96800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2906,65 +2992,68 @@
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E42" s="3">
         <v>254100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>254600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>418600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>473300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>345500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>293000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>303600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>244700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>445800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>500500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>617700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>698000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>754400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>691000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>257100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>297700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>374700</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2980,65 +3069,68 @@
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E43" s="3">
         <v>70400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>86500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>92700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>87300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>104900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>121100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>106800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>121100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>118200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>117300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>102000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>85700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>72500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>76100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3054,34 +3146,37 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>3100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3122,71 +3217,74 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>4</v>
+      <c r="Y44" s="3">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
         <v>29600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>65200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>118400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>194100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6600</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3202,65 +3300,68 @@
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>751400</v>
+      </c>
+      <c r="E46" s="3">
         <v>819700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>803200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>848400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>899400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>907600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>987200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1055500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1031900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1053900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>999600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1124800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1150800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1183400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1096600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1206600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>517800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>536200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3276,49 +3377,52 @@
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4100</v>
       </c>
       <c r="I47" s="3">
         <v>4100</v>
       </c>
       <c r="J47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K47" s="3">
         <v>4400</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>1700</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2600</v>
       </c>
       <c r="O47" s="3">
         <v>2600</v>
       </c>
       <c r="P47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="Q47" s="3">
         <v>2800</v>
@@ -3326,8 +3430,8 @@
       <c r="R47" s="3">
         <v>2800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>2800</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
@@ -3350,65 +3454,68 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3424,65 +3531,68 @@
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E49" s="3">
         <v>26300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>44200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>43500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>44500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3800</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3658,53 +3777,53 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>1100</v>
       </c>
       <c r="H52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>125100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>106400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>785400</v>
+      </c>
+      <c r="E54" s="3">
         <v>856600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>840600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>905100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>958300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>966000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1052600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1107400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1079400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1102500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1162900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1168500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1215800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1241800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1221100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1249000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>523600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>542800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E57" s="3">
         <v>128500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>127100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>143100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>150100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>132000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>159000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>129200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>127500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>168700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>142300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>141700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>114800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>107200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>86400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>57700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3998,37 +4128,40 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>9700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4066,71 +4199,74 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E59" s="3">
         <v>63100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>84000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>87800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>128100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>137400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>125400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>118200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>120300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>113100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>90900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>67400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4146,65 +4282,68 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E60" s="3">
         <v>233600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>231100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>262000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>274400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>262000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>288300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>282600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>257300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>264900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>294100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>260500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>262000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>227900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>202300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>177200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>141200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>125100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4220,35 +4359,38 @@
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>500</v>
       </c>
       <c r="H61" s="3">
         <v>500</v>
       </c>
       <c r="I61" s="3">
+        <v>500</v>
+      </c>
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4294,65 +4436,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7100</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E66" s="3">
         <v>237200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>235000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>280800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>295300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>283200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>315500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>302100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>282300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>289200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>319100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>285700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>286400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>245200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>209800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>184300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>141200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>125200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,14 +5058,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>1098500</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1127600</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4908,14 +5075,17 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-      <c r="Y70" s="3" t="s">
-        <v>4</v>
+      <c r="Y70" s="3">
+        <v>0</v>
       </c>
       <c r="Z70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>-1216200</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1232100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1228100</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-1227700</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1147700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1108400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-867300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>-688800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-694400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>566700</v>
+      </c>
+      <c r="E76" s="3">
         <v>611500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>593400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>608500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>648700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>670700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>726900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>797700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>797100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>813200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>843800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>882700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>929400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>996600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1011300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1064700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-716100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-709900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-67700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-85400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-52900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-45600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-71100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-41300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-42500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-57900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-62300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5639,8 +5837,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5672,8 +5870,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6083,8 +6299,8 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -6116,8 +6332,8 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6185,8 +6405,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6218,8 +6438,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6407,8 +6636,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -6440,8 +6669,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6805,8 +7050,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6838,8 +7083,8 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
@@ -6853,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,8 +7127,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6912,8 +7160,8 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
@@ -6927,31 +7175,34 @@
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -6986,8 +7237,8 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
@@ -6999,6 +7250,9 @@
         <v>4</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E8" s="3">
         <v>117700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>120500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>128500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>133100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>160500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>144000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>144700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>157100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>126000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>116200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>103300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>140700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>117100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>90700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>68700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>72400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>55900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E9" s="3">
         <v>43600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>57800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>65600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>64900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>66500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>68400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>64600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>60700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>56700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>74500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>56700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>37200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>29500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>47500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14100</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E10" s="3">
         <v>74100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>76600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>75300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>94900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>61400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>55600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>60400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>53500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>39200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>46400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>12400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13000</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E12" s="3">
         <v>20100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12900</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1212,8 +1232,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1254,14 +1274,17 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,13 +1292,13 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
+        <v>800</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>900</v>
       </c>
       <c r="H15" s="3">
         <v>900</v>
@@ -1284,14 +1307,14 @@
         <v>900</v>
       </c>
       <c r="J15" s="3">
+        <v>900</v>
+      </c>
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1331,14 +1354,17 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>107800</v>
+      </c>
+      <c r="E17" s="3">
         <v>116100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>132500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>153800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>164200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>185700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>188100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>189100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>187500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>164500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>180300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>193400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>162900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>140600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>117900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>86900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>74900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>61700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>77200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-48000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-45100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-64000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-90100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-45800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-49800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-49200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-33300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-42700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,115 +1579,119 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E21" s="3">
         <v>6800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-17900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-44400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-44500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1676,32 +1713,35 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-9700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-34200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1729,8 +1769,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1771,168 +1811,177 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>11500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-38200</v>
       </c>
       <c r="J23" s="3">
         <v>-38200</v>
       </c>
       <c r="K23" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="L23" s="3">
         <v>-25400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-66800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-85100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-45400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-43900</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>400</v>
       </c>
       <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>11800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-41100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-67700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-85400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-38400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-46600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-41500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-67700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-85400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-38400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-71100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-41300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-42500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-57900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-62300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2310,14 +2371,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>4</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-41500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-67700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-85400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-38400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-71100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-41300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-42500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-57900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-62300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-41500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-67700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-85400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-38400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-71100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-41300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-42500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-57900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-62300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>446500</v>
+      </c>
+      <c r="E41" s="3">
         <v>547900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>458200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>434800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>303900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>297100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>429400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>556200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>607300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>638100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>469400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>312700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>332700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>297900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>208600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>125700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>862500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>133300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>96800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2995,68 +3082,71 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E42" s="3">
         <v>117700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>254100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>254600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>418600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>473300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>345500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>293000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>303600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>244700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>445800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>500500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>617700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>698000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>754400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>691000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>257100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>297700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>374700</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3072,68 +3162,71 @@
       <c r="AA42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E43" s="3">
         <v>67300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>86500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>92700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>87300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>104900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>106800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>121100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>118200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>117300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>102000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>85700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>72500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>76100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3149,37 +3242,40 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3">
         <v>4200</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
         <v>3100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3220,74 +3316,77 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>4</v>
+      <c r="Z44" s="3">
+        <v>0</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E45" s="3">
         <v>4600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>45300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>65200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>56200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>118400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>194100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3303,68 +3402,71 @@
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>711500</v>
+      </c>
+      <c r="E46" s="3">
         <v>751400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>819700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>803200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>848400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>899400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>907600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>987200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1055500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1031900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1053900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>999600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1124800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1150800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1183400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1096600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1206600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>517800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>536200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3380,52 +3482,55 @@
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E47" s="3">
         <v>7000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4100</v>
       </c>
       <c r="J47" s="3">
         <v>4100</v>
       </c>
       <c r="K47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L47" s="3">
         <v>4400</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>1700</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2600</v>
       </c>
       <c r="P47" s="3">
         <v>2600</v>
       </c>
       <c r="Q47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="R47" s="3">
         <v>2800</v>
@@ -3433,8 +3538,8 @@
       <c r="S47" s="3">
         <v>2800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>2800</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
@@ -3457,68 +3562,71 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3534,68 +3642,71 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E49" s="3">
         <v>24800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>44200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>43500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>44500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3800</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,13 +3882,16 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -3780,53 +3900,53 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>1100</v>
       </c>
       <c r="I52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>125100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>106400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>783200</v>
+      </c>
+      <c r="E54" s="3">
         <v>785400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>856600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>840600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>905100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>958300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>966000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1052600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1107400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1079400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1102500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1162900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1168500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1215800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1241800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1221100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1249000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>523600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>542800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E57" s="3">
         <v>115400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>128500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>127100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>143100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>150100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>132000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>159000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>148800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>129200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>127500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>168700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>142300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>141700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>114800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>107200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>86400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4131,40 +4262,43 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4202,74 +4336,77 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E59" s="3">
         <v>46300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>61000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>87800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>137400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>125400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>118200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>120300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>113100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>95100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>90900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>67400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4285,68 +4422,71 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E60" s="3">
         <v>208900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>233600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>231100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>262000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>274400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>262000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>288300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>282600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>257300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>264900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>294100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>260500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>262000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>227900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>202300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>177200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>141200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>125100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4362,38 +4502,41 @@
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>500</v>
       </c>
       <c r="I61" s="3">
         <v>500</v>
       </c>
       <c r="J61" s="3">
+        <v>500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4448,59 +4594,59 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
+        <v>500</v>
+      </c>
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7100</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E66" s="3">
         <v>210600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>237200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>235000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>280800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>295300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>283200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>315500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>302100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>282300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>289200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>319100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>285700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>286400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>245200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>209800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>184300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>141200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>125200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5061,14 +5229,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1098500</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1127600</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5078,14 +5246,17 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-      <c r="Z70" s="3" t="s">
-        <v>4</v>
+      <c r="Z70" s="3">
+        <v>0</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1216200</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
         <v>-1232100</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1227700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1147700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1108400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-867300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3">
         <v>-688800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-694400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>564500</v>
+      </c>
+      <c r="E76" s="3">
         <v>566700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>611500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>593400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>608500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>648700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>670700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>726900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>797700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>797100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>813200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>843800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>882700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>929400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>996600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1011300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1064700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-716100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-709900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-41500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-67700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-85400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-38400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-71100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-41300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-42500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-57900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-62300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5840,8 +6039,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5873,8 +6072,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,8 +6487,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6302,8 +6519,8 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -6335,8 +6552,8 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6408,8 +6629,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6441,8 +6662,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6639,8 +6869,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -6672,8 +6902,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7267,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7053,8 +7299,8 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -7086,8 +7332,8 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7130,8 +7379,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7163,8 +7412,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>4</v>
@@ -7178,8 +7427,11 @@
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7204,8 +7456,8 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -7240,8 +7492,8 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>4</v>
@@ -7253,6 +7505,9 @@
         <v>4</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>ZH</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E8" s="3">
         <v>92600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>100100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>117700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>120500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>128500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>133100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>140100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>144000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>144700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>157100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>126000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>116200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>103300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>140700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>117100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>90700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>68700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>72400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>55900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>38500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27100</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E9" s="3">
         <v>35900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>37500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>57800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>65600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>64900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>66500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>70200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>64600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>60700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>56700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>74500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>56700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>37200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E10" s="3">
         <v>56700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>62200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>74100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>77000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>76600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>94900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>75200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>61400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>66300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>60400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>53500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>39200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>46400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E12" s="3">
         <v>16100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>31100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>15300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>24600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,13 +1259,16 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>18100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1281,8 +1300,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1323,37 +1342,40 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>800</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
       </c>
       <c r="H15" s="3">
+        <v>800</v>
+      </c>
+      <c r="I15" s="3">
         <v>900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>900</v>
@@ -1362,14 +1384,14 @@
         <v>900</v>
       </c>
       <c r="M15" s="3">
+        <v>900</v>
+      </c>
+      <c r="N15" s="3">
         <v>800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1409,14 +1431,17 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E17" s="3">
         <v>106600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>112800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>107800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>116100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>132500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>164200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>185700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>188100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>189100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>176300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>187500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>164500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>180300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>193400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>192500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>162900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>140600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>117900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>86900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>74900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>61700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>77200</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-25300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-25100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-48000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-45100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-64000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-90100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-51800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-45800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-49800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-49200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-14500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-33300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-42700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,133 +1680,137 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5400</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-28500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-44400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-44500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1796,32 +1832,35 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>-9700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-34200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1858,8 +1897,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1900,186 +1939,195 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-38200</v>
       </c>
       <c r="M23" s="3">
         <v>-38200</v>
       </c>
       <c r="N23" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-25400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-85100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-52500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-45400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-46600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-37300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-43900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>400</v>
       </c>
       <c r="P24" s="3">
         <v>400</v>
       </c>
       <c r="Q24" s="3">
+        <v>400</v>
+      </c>
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-67700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-85400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-52900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-38400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-45600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-46600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-17100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-31800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-37300</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-22800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-67700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-85400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-52900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-45600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-71100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-36200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-62300</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2502,14 +2562,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-22800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-67700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-85400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-52900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-45600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-71100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-36200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-62300</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-22800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-67700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-85400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-52900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-45600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-71100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-36200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-62300</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>481700</v>
+      </c>
+      <c r="E41" s="3">
         <v>383500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>446500</v>
       </c>
       <c r="F41" s="3">
         <v>446500</v>
       </c>
       <c r="G41" s="3">
+        <v>446500</v>
+      </c>
+      <c r="H41" s="3">
         <v>547900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>458200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>434800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>303900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>297100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>429400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>556200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>607300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>638100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>469400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>312700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>332700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>297900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>208600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>125700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>862500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>133300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>96800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3265,77 +3351,80 @@
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E42" s="3">
         <v>230700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>197000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>181300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>117700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>254100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>254600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>418600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>473300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>345500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>293000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>303600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>244700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>445800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>500500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>617700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>698000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>754400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>691000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>257100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>297700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>374700</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,77 +3440,80 @@
       <c r="AD42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E43" s="3">
         <v>49200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>56700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>86500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>92700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>87300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>104900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>113200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>121100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>106800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>121100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>118200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>117300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>102000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>85700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>72500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>76100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3437,46 +3529,49 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>4200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>2600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>3100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3517,83 +3612,86 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>4</v>
+      <c r="AC44" s="3">
+        <v>0</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
         <v>20900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>65200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>56200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>37600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>118400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>194100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3609,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>676500</v>
+      </c>
+      <c r="E46" s="3">
         <v>684400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>715500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>711500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>751400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>819700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>803200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>848400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>899400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>907600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>987200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1055500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1031900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1053900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>999600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1124800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1150800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1183400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1096600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1206600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>517800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>536200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3695,61 +3796,64 @@
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E47" s="3">
         <v>56200</v>
       </c>
-      <c r="E47" s="3">
-        <v>23100</v>
-      </c>
       <c r="F47" s="3">
+        <v>52400</v>
+      </c>
+      <c r="G47" s="3">
         <v>35900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>4100</v>
       </c>
       <c r="M47" s="3">
         <v>4100</v>
       </c>
       <c r="N47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O47" s="3">
         <v>4400</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>1700</v>
-      </c>
-      <c r="R47" s="3">
-        <v>2600</v>
       </c>
       <c r="S47" s="3">
         <v>2600</v>
       </c>
       <c r="T47" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="U47" s="3">
         <v>2800</v>
@@ -3757,8 +3861,8 @@
       <c r="V47" s="3">
         <v>2800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
+      <c r="W47" s="3">
+        <v>2800</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
@@ -3781,77 +3885,80 @@
       <c r="AD47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3867,77 +3974,80 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E49" s="3">
         <v>23900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>42700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>44200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>43500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>44500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>29300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3800</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,22 +4241,25 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
-        <v>30500</v>
-      </c>
       <c r="F52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G52" s="3">
         <v>1200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -4149,53 +4268,53 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>1100</v>
       </c>
       <c r="L52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>125100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>24800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>106400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>742100</v>
+      </c>
+      <c r="E54" s="3">
         <v>772800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>802200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>783200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>785400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>856600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>840600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>905100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>958300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>966000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1052600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1107400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1079400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1102500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1162900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1168500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1215800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1241800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1221100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1249000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>523600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>542800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>99700</v>
+      </c>
+      <c r="E57" s="3">
         <v>96900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>106400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>102800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>115400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>128500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>127100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>143100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>150100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>132000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>159000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>148800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>129200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>127500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>168700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>142300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>141700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>114800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>107200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>86400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>69900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>57700</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4533,49 +4663,52 @@
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E58" s="3">
         <v>18300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>28200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4613,83 +4746,86 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>4</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E59" s="3">
         <v>47900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>63100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>68200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>87800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>137400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>125400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>118200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>120300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>113100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>95100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>90900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>67400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4705,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E60" s="3">
         <v>185500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>205700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>203800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>208900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>233600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>231100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>262000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>274400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>262000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>288300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>282600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>257300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>264900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>294100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>260500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>262000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>227900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>202300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>177200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>141200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>125100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4791,47 +4930,50 @@
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>500</v>
       </c>
       <c r="L61" s="3">
         <v>500</v>
       </c>
       <c r="M61" s="3">
+        <v>500</v>
+      </c>
+      <c r="N61" s="3">
         <v>2700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4877,13 +5019,16 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
@@ -4895,59 +5040,59 @@
         <v>500</v>
       </c>
       <c r="H62" s="3">
+        <v>500</v>
+      </c>
+      <c r="I62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7100</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E66" s="3">
         <v>193800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>214800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>210000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>210600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>237200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>235000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>280800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>295300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>283200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>315500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>302100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>282300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>289200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>319100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>285700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>286400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>245200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>209800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>184300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>141200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>125200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5574,14 +5741,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>1098500</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1127600</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5591,14 +5758,17 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-      <c r="AC70" s="3" t="s">
-        <v>4</v>
+      <c r="AC70" s="3">
+        <v>0</v>
       </c>
       <c r="AD70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>-1296800</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1230500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1216200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1232100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1227700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1147700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1108400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-1026300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>-867300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X72" s="3">
         <v>-688800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-694400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>543900</v>
+      </c>
+      <c r="E76" s="3">
         <v>569100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>578100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>564500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>566700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>611500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>593400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>608500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>648700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>670700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>726900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>797700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>797100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>813200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>843800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>882700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>929400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>996600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1011300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1064700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-716100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-709900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-22800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-67700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-85400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-52900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-45600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-71100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-36200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-62300</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6446,8 +6644,8 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -6479,8 +6677,8 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,8 +7137,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6962,8 +7178,8 @@
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P89" s="3">
         <v>0</v>
@@ -6995,8 +7211,8 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7080,8 +7300,8 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7113,8 +7333,8 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7526,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7338,8 +7567,8 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -7371,8 +7600,8 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7689,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,8 +8004,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7800,8 +8045,8 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -7833,8 +8078,8 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
@@ -7848,8 +8093,11 @@
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7886,8 +8134,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7919,8 +8167,8 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
@@ -7934,8 +8182,11 @@
       <c r="AD101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7969,8 +8220,8 @@
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -8005,8 +8256,8 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>4</v>
@@ -8018,6 +8269,9 @@
         <v>4</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
